--- a/data/argentina/p6_deployment/predicciones.xlsx
+++ b/data/argentina/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB17"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,40 +530,45 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>emergency_fill</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -572,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45506.83333333334</v>
+        <v>45513.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>newells old boys</t>
+          <t>dep  riestra</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>estudiantes l p</t>
+          <t>lanus</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,85 +610,88 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3621665319320938</v>
+        <v>0.2633204633204633</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3401778496362167</v>
+        <v>0.3057915057915058</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2976556184316896</v>
+        <v>0.4308880308880308</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0498709940249864</v>
+        <v>0.05490387748452275</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2998299420230756</v>
+        <v>0.314810907209819</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3808043616035225</v>
+        <v>0.4268456364859128</v>
       </c>
       <c r="S2" t="n">
-        <v>0.319365696373402</v>
+        <v>0.2583434563042682</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04062651196730582</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
+        <v>0.1210541306944071</v>
+      </c>
+      <c r="W2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.04062651196730582</v>
-      </c>
       <c r="X2" t="n">
-        <v>0.3808043616035225</v>
+        <v>0.1210541306944071</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z2" t="inlineStr">
+        <v>0.4268456364859128</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA2" t="n">
-        <v>2.48222191201277</v>
-      </c>
       <c r="AB2" t="n">
-        <v>2.48222191201277</v>
+        <v>2.782335757581222</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.782335757581222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45507.625</v>
+        <v>45513.6875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>barracas central</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>argentinos jrs</t>
+          <t>talleres cordoba</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -703,85 +711,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2575250836120401</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2887402452619844</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4537346711259755</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04949104949104943</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2812126375785755</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.3986549730147383</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3201323894066863</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0.1099147277527538</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.1099147277527538</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3986549730147383</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.3</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.3865105008077544</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.326534733441034</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.2869547657512116</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.05602115454332202</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.3922360350678503</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.3723937150840167</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.2353702498481329</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.005725534260095921</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.005725534260095921</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.3922360350678503</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA3" t="n">
-        <v>2.556737734900516</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.556737734900516</v>
+        <v>2.598578716859133</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.598578716859133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45507.625</v>
+        <v>45513.79166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>velez sarsfield</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>defensa y justicia</t>
+          <t>union de santa fe</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -801,85 +810,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4982964224872232</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2913117546848382</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2103918228279387</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0562303193882141</v>
+        <v>0.03703703703703698</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4131204899825422</v>
+        <v>0.3838045737277082</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3757126168253053</v>
+        <v>0.347558830247032</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2111668931921525</v>
+        <v>0.2686365960252598</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>-0.08517593250468092</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0.0623760022991367</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.08517593250468092</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4131204899825422</v>
+        <v>0.0623760022991367</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z4" t="inlineStr">
+        <v>0.3838045737277082</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA4" t="n">
-        <v>2.692870239768369</v>
-      </c>
       <c r="AB4" t="n">
-        <v>2.692870239768369</v>
+        <v>2.501778390420687</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.501778390420687</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45507.71875</v>
+        <v>45513.875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>talleres cordoba</t>
+          <t>racing club</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>gimnasia l p</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -899,85 +909,86 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4745960470954284</v>
+        <v>0.5925155925155925</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3061909981260828</v>
+        <v>0.2494802494802495</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2192129547784888</v>
+        <v>0.158004158004158</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0535275273783804</v>
+        <v>0.05482456140350878</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4190933307370652</v>
+        <v>0.5015153804004705</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3813079638093982</v>
+        <v>0.3424639074186733</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1995987054535366</v>
+        <v>0.1560207121808563</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>-0.05550271635836312</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>-0.09100021211512199</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.05550271635836312</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4190933307370652</v>
+        <v>-0.09100021211512199</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="inlineStr">
+        <v>0.5015153804004705</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA5" t="n">
-        <v>2.731803397296843</v>
-      </c>
       <c r="AB5" t="n">
-        <v>2.731803397296843</v>
+        <v>3.269060420420227</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.269060420420227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45507.80208333334</v>
+        <v>45514.60416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>san lorenzo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>san lorenzo</t>
+          <t>atl  tucuman</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1018,64 +1029,65 @@
         <v>0.05126050420168071</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3612126570817278</v>
+        <v>0.408570664041806</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3878453149304889</v>
+        <v>0.4015632082037098</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2509420279877833</v>
+        <v>0.1898661277544841</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.04811709750442977</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.02807506052461972</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04811709750442977</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3878453149304889</v>
+        <v>0.02807506052461972</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z6" t="inlineStr">
+        <v>0.408570664041806</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA6" t="n">
-        <v>2.528117417400525</v>
-      </c>
       <c r="AB6" t="n">
-        <v>2.528117417400525</v>
+        <v>2.663212812530973</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.663212812530973</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45507.85416666666</v>
+        <v>45514.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>huracan</t>
+          <t>rosario central</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>racing club</t>
+          <t>newells old boys</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1095,85 +1107,86 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3366583541147132</v>
+        <v>0.3884093711467324</v>
       </c>
       <c r="M7" t="n">
-        <v>0.314214463840399</v>
+        <v>0.345252774352651</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3491271820448877</v>
+        <v>0.2663378545006165</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06084656084656093</v>
+        <v>0.07275132275132279</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2605852456168034</v>
+        <v>0.4037640024404929</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4057049926464068</v>
+        <v>0.3919499425440674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3337097617367898</v>
+        <v>0.2042860550154396</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0.09149052880600783</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.01535463129376052</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09149052880600783</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4057049926464068</v>
+        <v>0.01535463129376052</v>
       </c>
       <c r="Y7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z7" t="inlineStr">
+        <v>0.4037640024404929</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA7" t="n">
-        <v>2.644533319732269</v>
-      </c>
       <c r="AB7" t="n">
-        <v>2.644533319732269</v>
+        <v>2.631881236652564</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.631881236652564</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45508.625</v>
+        <v>45514.78125</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sarmiento junin</t>
+          <t>ind  rivadavia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1193,85 +1206,88 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3446153846153846</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3323076923076923</v>
+        <v>0.3146067415730338</v>
       </c>
       <c r="N8" t="n">
-        <v>0.323076923076923</v>
+        <v>0.4494382022471911</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07473544973544977</v>
+        <v>0.05952380952380931</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3232892768906198</v>
+        <v>0.3409693117441649</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3971623748008928</v>
+        <v>0.4125045037664627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2795483483084874</v>
+        <v>0.2465261844893724</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06485468249320048</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
+        <v>0.09789776219342894</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" t="n">
-        <v>0.06485468249320048</v>
-      </c>
       <c r="X8" t="n">
-        <v>0.3971623748008928</v>
+        <v>0.09789776219342894</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z8" t="inlineStr">
+        <v>0.4125045037664627</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA8" t="n">
-        <v>2.58884941655218</v>
-      </c>
       <c r="AB8" t="n">
-        <v>2.58884941655218</v>
+        <v>2.688855016632237</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.688855016632237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45508.625</v>
+        <v>45514.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>union de santa fe</t>
+          <t>river plate</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>river plate</t>
+          <t>huracan</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1291,85 +1307,86 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.263456090651558</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2974504249291784</v>
+        <v>0.2644230769230769</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4390934844192634</v>
+        <v>0.1586538461538461</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08448540706605234</v>
+        <v>0.05050505050505061</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2096663114551144</v>
+        <v>0.5523514664806761</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4024223557619477</v>
+        <v>0.314221184240728</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3879113327829379</v>
+        <v>0.1334273492785959</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0.1049719308327692</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.02457161044240075</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1049719308327692</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4024223557619477</v>
+        <v>-0.02457161044240075</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z9" t="inlineStr">
+        <v>0.5523514664806761</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA9" t="n">
-        <v>2.623135893585482</v>
-      </c>
       <c r="AB9" t="n">
-        <v>2.623135893585482</v>
+        <v>3.600428596608907</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.600428596608907</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45508.72916666666</v>
+        <v>45515.625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>boca juniors</t>
+          <t>central cordoba</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>defensa y justicia</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1389,85 +1406,86 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6780025828669823</v>
+        <v>0.3324808184143222</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2195436934997848</v>
+        <v>0.29923273657289</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1024537236332329</v>
+        <v>0.3682864450127877</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08450046685340795</v>
+        <v>0.0443376068376069</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5581727578696175</v>
+        <v>0.3461543407562248</v>
       </c>
       <c r="R10" t="n">
-        <v>0.329031016596523</v>
+        <v>0.3741134572753897</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1127962255338595</v>
+        <v>0.2797322019683854</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>-0.1198298249973648</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0.07488072070249974</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1198298249973648</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5581727578696175</v>
+        <v>0.07488072070249974</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z10" t="inlineStr">
+        <v>0.3741134572753897</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA10" t="n">
-        <v>3.638373900021387</v>
-      </c>
       <c r="AB10" t="n">
-        <v>3.638373900021387</v>
+        <v>2.438608153849558</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.438608153849558</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45508.83333333334</v>
+        <v>45515.625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>atl  tucuman</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ind  rivadavia</t>
+          <t>platense</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1490,64 +1508,83 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.463395937140667</v>
+        <v>0.4759206798866855</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2989651207359141</v>
+        <v>0.2974504249291784</v>
       </c>
       <c r="N11" t="n">
-        <v>0.237638942123419</v>
+        <v>0.226628895184136</v>
       </c>
       <c r="O11" t="n">
-        <v>0.07899090157154665</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+        <v>0.05059523809523814</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3572735029190396</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4210473676177651</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2216791294631952</v>
+      </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+        <v>0.1235969426885867</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1235969426885867</v>
+      </c>
       <c r="Y11" t="n">
-        <v>1.322033898305085</v>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+        <v>0.4210473676177651</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.744540523367905</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.744540523367905</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45508.83333333334</v>
+        <v>45515.72916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lanus</t>
+          <t>banfield</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tigre</t>
+          <t>velez sarsfield</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1567,85 +1604,86 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="L12" t="n">
-        <v>0.535588324769581</v>
+        <v>0.3077851538925769</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2504237302301013</v>
+        <v>0.3180446590223295</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2139879450003176</v>
+        <v>0.3741701870850936</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07925183456828533</v>
+        <v>0.04807084123972172</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4625448323626192</v>
+        <v>0.2843166418583077</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3671591776865472</v>
+        <v>0.4152683438416073</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1702959899508336</v>
+        <v>0.300415014300085</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>-0.07304349240696173</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0.09722368481927779</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.07304349240696173</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4625448323626192</v>
+        <v>0.09722368481927779</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z12" t="inlineStr">
+        <v>0.4152683438416073</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA12" t="n">
-        <v>3.0150361549014</v>
-      </c>
       <c r="AB12" t="n">
-        <v>3.0150361549014</v>
+        <v>2.706870735693159</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.706870735693159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45509.60416666666</v>
+        <v>45515.83333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dep  riestra</t>
+          <t>estudiantes l p</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>central cordoba</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1665,67 +1703,86 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4887272727272727</v>
+        <v>0.4853128991060026</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2901818181818182</v>
+        <v>0.3154533844189016</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2210909090909091</v>
+        <v>0.1992337164750957</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07691102756892221</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+        <v>0.05668016194331993</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3912313480791806</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.383862063564299</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2249065883565203</v>
+      </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+        <v>-0.09408155102682197</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.09408155102682197</v>
+      </c>
       <c r="Y13" t="n">
-        <v>1.308196721311476</v>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+        <v>0.3912313480791806</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.550188818161515</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.550188818161515</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45509.70833333334</v>
+        <v>45516.79166666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gimnasia l p</t>
+          <t>tigre</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>rosario central</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1745,320 +1802,67 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
         <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4333067092651757</v>
+        <v>0.3293021735577709</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3005191693290735</v>
+        <v>0.305932341885929</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2661741214057508</v>
+        <v>0.3647654845563</v>
       </c>
       <c r="O14" t="n">
-        <v>0.07341120994534345</v>
+        <v>0.05441825199889716</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3049874164115554</v>
+        <v>0.2565871634467294</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4029691497903346</v>
+        <v>0.3822209701549344</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2920434337981102</v>
+        <v>0.3611918663983362</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.1024499804612611</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
+        <v>0.07628862826900534</v>
+      </c>
+      <c r="W14" t="n">
         <v>0</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.1024499804612611</v>
-      </c>
       <c r="X14" t="n">
-        <v>0.4029691497903346</v>
+        <v>0.07628862826900534</v>
       </c>
       <c r="Y14" t="n">
+        <v>0.3822209701549344</v>
+      </c>
+      <c r="Z14" t="n">
         <v>3.1</v>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA14" t="n">
-        <v>2.626700096770825</v>
-      </c>
       <c r="AB14" t="n">
-        <v>2.626700096770825</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>65Xumenk</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45509.83333333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>platense</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>banfield</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" t="n">
-        <v>61</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>argentina</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>liga profesional</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3569296375266524</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.3437100213219616</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.2993603411513859</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.0775664001470453</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.3524454246090371</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.392878581254653</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2546759941363099</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.04916855993269137</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.04916855993269137</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.392878581254653</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.560926085626453</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.560926085626453</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SvlzcWFD</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45512.625</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>argentinos jrs</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>sarmiento junin</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>61</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>argentina</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>liga profesional</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.4757220707350898</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3578840423168462</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.1663938869480639</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="n">
-        <v>0.5242779292649102</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.41743502759818</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.41743502759818</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ngdGLTFj</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45510.88194444445</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>san lorenzo</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>velez sarsfield</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>64</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>argentina</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>copa argentina</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.5181971723886001</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.1302043934446169</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.351598434166783</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="n">
-        <v>0.4818028276113999</v>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.140566801626847</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.140566801626847</v>
+        <v>2.491455883945897</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.491455883945897</v>
       </c>
     </row>
   </sheetData>
